--- a/tolerance_analysis/tol_config_模板.xlsx
+++ b/tolerance_analysis/tol_config_模板.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>6. 运行参数中 保存TSC 始终为 Y；保存WorstCase/BestCase 由用户选择 Y/N。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7. 后焦补偿面留空=不加 TDE 补偿器；填面号则在该面厚度加 COMP，</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   补偿Min/Max 留空时由 Zemax 自由调整，补偿线对为补偿专用 MF 的 GMTA 频率。</t>
         </is>
       </c>
     </row>
@@ -535,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -657,83 +671,137 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>保存TSC</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>后焦补偿面</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>始终保存</t>
+          <t>COMP 补偿面号；留空=不加补偿器</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>保存WorstCase</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>补偿Min</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>保存最差案例文件</t>
+          <t>补偿下限；留空=Zemax 自由调整</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>保存BestCase</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>补偿Max</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>保存最佳案例文件</t>
+          <t>补偿上限；留空=Zemax 自由调整</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>输出统计Excel</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+          <t>补偿线对</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>本期预留，默认关</t>
+          <t>补偿专用 MF 的 GMTA 频率 lp/mm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>保存TSC</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>始终保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>保存WorstCase</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>保存最差案例文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>保存BestCase</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>保存最佳案例文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>输出统计Excel</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>本期预留，默认关</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>输出直方图</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>本期预留，默认关</t>
         </is>
@@ -750,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -872,83 +940,137 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>保存TSC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>后焦补偿面</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>始终保存</t>
+          <t>COMP 补偿面号；留空=不加补偿器</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>保存WorstCase</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>补偿Min</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>保存最差案例文件</t>
+          <t>补偿下限；留空=Zemax 自由调整</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>保存BestCase</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>补偿Max</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>保存最佳案例文件</t>
+          <t>补偿上限；留空=Zemax 自由调整</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>输出统计Excel</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+          <t>补偿线对</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>34</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>本期预留，默认关</t>
+          <t>补偿专用 MF 的 GMTA 频率 lp/mm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>保存TSC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>始终保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>保存WorstCase</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>保存最差案例文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>保存BestCase</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>保存最佳案例文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>输出统计Excel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>本期预留，默认关</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>输出直方图</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>本期预留，默认关</t>
         </is>

--- a/tolerance_analysis/tol_config_模板.xlsx
+++ b/tolerance_analysis/tol_config_模板.xlsx
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>本期预留，默认关</t>
+          <t>Y=导出ZTD统计Excel，含百分位与Cpk1.33规格限</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>本期预留，默认关</t>
+          <t>Y=导出ZTD统计Excel，含百分位与Cpk1.33规格限</t>
         </is>
       </c>
     </row>
